--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6717,6 +6717,78 @@
         <v>0</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SHIVAM TRADERS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SHIVAM TRADERS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>THE TOYS HOME</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>THE TOYS HOME</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MOHINI COLLECTION EXT</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MOHINI COLLECTION EXT</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6789,6 +6789,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S V GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S V GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6813,6 +6813,54 @@
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SARDAR JI TOYS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SARDAR JI TOYS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6837,30 +6837,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.4762</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.5339</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5976,22 +5976,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+          <t>R &amp; S ENTERPRISES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+          <t>R &amp; S ENTERPRISES</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -6000,22 +6000,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R &amp; S ENTERPRISES</t>
+          <t>ELARA AND COMPANY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R &amp; S ENTERPRISES</t>
+          <t>ELARA AND COMPANY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -6024,22 +6024,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ELARA AND COMPANY</t>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ELARA AND COMPANY</t>
+          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -6048,22 +6048,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+          <t>MAA ENTERPRISES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SPILLBOX INNOVATION PRIVATE LIMITED</t>
+          <t>MAA ENTERPRISES</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -6072,12 +6072,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAA ENTERPRISES</t>
+          <t>BANSAL BOOK AND STATIONERS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAA ENTERPRISES</t>
+          <t>BANSAL BOOK AND STATIONERS</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6096,12 +6096,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BANSAL BOOK AND STATIONERS</t>
+          <t>TOYS TOWN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BANSAL BOOK AND STATIONERS</t>
+          <t>TOYS TOWN</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6120,12 +6120,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOYS TOWN</t>
+          <t>SHREE BALAJI ENTERPRISES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOYS TOWN</t>
+          <t>SHREE BALAJI ENTERPRISES</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -6144,12 +6144,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SHREE BALAJI ENTERPRISES</t>
+          <t>BABA SALES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SHREE BALAJI ENTERPRISES</t>
+          <t>BABA SALES</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6168,12 +6168,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>EQUATOR TRADE HOUSE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BABA SALES</t>
+          <t>EQUATOR TRADE HOUSE</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -6192,12 +6192,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EQUATOR TRADE HOUSE</t>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EQUATOR TRADE HOUSE</t>
+          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -6216,12 +6216,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+          <t>TEJAL INTERNATIONAL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>THEME AMBIENCE ENTERPRISES PRIVATE LIMITED</t>
+          <t>TEJAL INTERNATIONAL</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -6240,12 +6240,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MILLENNIUM INTERNATIONAL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TEJAL INTERNATIONAL</t>
+          <t>MILLENNIUM INTERNATIONAL</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -6264,22 +6264,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MILLENNIUM INTERNATIONAL</t>
+          <t>SK ENTERPRISE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MILLENNIUM INTERNATIONAL</t>
+          <t>SK ENTERPRISE</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.4762</v>
+        <v>0.4972</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5339</v>
+        <v>0.5744</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -6288,22 +6288,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK ENTERPRISE</t>
+          <t>SHUBHAM ENTERPRISES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK ENTERPRISE</t>
+          <t>SHUBHAM ENTERPRISES</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.4972</v>
+        <v>0.4762</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5744</v>
+        <v>0.5339</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -6312,22 +6312,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SHUBHAM ENTERPRISES</t>
+          <t>ANAND GIFT EMPORIUM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHUBHAM ENTERPRISES</t>
+          <t>ANAND GIFT EMPORIUM</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -6336,22 +6336,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ANAND GIFT EMPORIUM</t>
+          <t>RAJESH TRADERS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ANAND GIFT EMPORIUM</t>
+          <t>RAJESH TRADERS</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -6360,12 +6360,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RAJESH TRADERS</t>
+          <t>VIJAY SALES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RAJESH TRADERS</t>
+          <t>VIJAY SALES</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -6384,22 +6384,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VIJAY SALES</t>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VIJAY SALES</t>
+          <t>ZIPPYCUBS PRIVATE LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -6408,22 +6408,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+          <t>SEEMA AND SONS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZIPPYCUBS PRIVATE LIMITED</t>
+          <t>SEEMA AND SONS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.5238</v>
+        <v>0.4738</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5763</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6432,22 +6432,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEEMA AND SONS</t>
+          <t>AGGARWAL MARKETING CO.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SEEMA AND SONS</t>
+          <t>AGGARWAL MARKETING CO.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.4738</v>
+        <v>0.4308</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5072</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -6456,22 +6456,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AGGARWAL MARKETING CO.</t>
+          <t>H S ENTERPRISES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AGGARWAL MARKETING CO.</t>
+          <t>H S ENTERPRISES</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.4308</v>
+        <v>0.4762</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5072</v>
+        <v>0.5339</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -6480,12 +6480,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>H S ENTERPRISES</t>
+          <t>MODERN AGENCIES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H S ENTERPRISES</t>
+          <t>MODERN AGENCIES</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -6504,12 +6504,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MODERN AGENCIES</t>
+          <t>PRINCE ENTERPRISES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MODERN AGENCIES</t>
+          <t>PRINCE ENTERPRISES</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -6528,22 +6528,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PRINCE ENTERPRISES</t>
+          <t>KIDS JUNCTION</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PRINCE ENTERPRISES</t>
+          <t>KIDS JUNCTION</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.4762</v>
+        <v>0.4286</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5339</v>
+        <v>0.4915</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -6552,22 +6552,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KIDS JUNCTION</t>
+          <t>SATNAM MARKETING</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KIDS JUNCTION</t>
+          <t>SATNAM MARKETING</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -6576,22 +6576,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SATNAM MARKETING</t>
+          <t>Ramdev Extension</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SATNAM MARKETING</t>
+          <t>Ramdev Extension</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.4762</v>
+        <v>0.4286</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5339</v>
+        <v>0.4915</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -6600,22 +6600,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ramdev Extension</t>
+          <t>T G ENTERPRISES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ramdev Extension</t>
+          <t>T G ENTERPRISES</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -6624,12 +6624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T G ENTERPRISES</t>
+          <t>RAMDEV IMPEX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>T G ENTERPRISES</t>
+          <t>RAMDEV IMPEX</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6648,22 +6648,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RAMDEV IMPEX</t>
+          <t>CENTER ONE ENTERPRISES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RAMDEV IMPEX</t>
+          <t>CENTER ONE ENTERPRISES</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -6672,22 +6672,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CENTER ONE ENTERPRISES</t>
+          <t>BLISS ENTERPRISES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CENTER ONE ENTERPRISES</t>
+          <t>BLISS ENTERPRISES</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.5238</v>
+        <v>0.4762</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5763</v>
+        <v>0.5339</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BLISS ENTERPRISES</t>
+          <t>SHIVAM TRADERS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BLISS ENTERPRISES</t>
+          <t>SHIVAM TRADERS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.4762</v>
+        <v>0.5238</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5339</v>
+        <v>0.5763</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -6720,22 +6720,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SHIVAM TRADERS</t>
+          <t>THE TOYS HOME</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SHIVAM TRADERS</t>
+          <t>THE TOYS HOME</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.5238</v>
+        <v>0.4286</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5763</v>
+        <v>0.4915</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -6744,22 +6744,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>THE TOYS HOME</t>
+          <t>MOHINI COLLECTION EXT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>THE TOYS HOME</t>
+          <t>MOHINI COLLECTION EXT</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.4286</v>
+        <v>0.4762</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4915</v>
+        <v>0.5339</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -6768,12 +6768,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MOHINI COLLECTION EXT</t>
+          <t>S V GIFTS &amp; TOYS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MOHINI COLLECTION EXT</t>
+          <t>S V GIFTS &amp; TOYS</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6792,48 +6792,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S V GIFTS &amp; TOYS</t>
+          <t>SARDAR JI TOYS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S V GIFTS &amp; TOYS</t>
+          <t>SARDAR JI TOYS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.4762</v>
+        <v>0.619</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5339</v>
+        <v>0.661</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>SARDAR JI TOYS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SARDAR JI TOYS</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="F56" t="n">
         <v>0</v>
       </c>
     </row>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6813,6 +6813,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RAMDEV STATIONERY SPORTS GIFTS &amp; TOYS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6837,6 +6837,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>KASHMIR BOOK DEPOT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KASHMIR BOOK DEPOT</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5482,7 +5482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6837,30 +6837,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>KASHMIR BOOK DEPOT</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>KASHMIR BOOK DEPOT</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.4286</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5469,6 +5469,33 @@
       </c>
       <c r="G177" t="n">
         <v>8906187980505</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>178</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SMRT1362</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>899</v>
+      </c>
+      <c r="D178" t="n">
+        <v>95030020</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SMRT1362</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>8906187980543</v>
       </c>
     </row>
   </sheetData>
@@ -5482,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6861,6 +6888,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SAI TAK AND CO (BOSTON BOOKS, STATIONERY &amp; TOYS) REKHA REKHAJA (BOSTON BOOKS, STATIONERY &amp; TOYS)- MN CAPITAL 7-</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -5509,7 +5509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6894,6 +6894,11 @@
           <t>SAI TAK AND CO (BOSTON BOOKS, STATIONERY &amp; TOYS) REKHA REKHAJA (BOSTON BOOKS, STATIONERY &amp; TOYS)- MN CAPITAL 7-</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MAYA TOYS</t>
+        </is>
+      </c>
       <c r="C58" t="n">
         <v>0.4286</v>
       </c>
@@ -6904,6 +6909,54 @@
         <v>0.4915</v>
       </c>
       <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JAI BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>JAI BALAJI ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>INTERVAL THE MAGIC LAMPS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>INTERVAL THE MAGIC LAMPS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="F60" t="n">
         <v>0</v>
       </c>
     </row>

--- a/master_price_list.xlsx
+++ b/master_price_list.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5497,6 +5497,35 @@
       <c r="G178" t="n">
         <v>8906187980543</v>
       </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>179</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SMRT9999</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>999</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>95030020</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>SMRT9999</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
